--- a/experiments/MSRV2_DATASET/model.xlsx
+++ b/experiments/MSRV2_DATASET/model.xlsx
@@ -1676,123 +1676,244 @@
       <c r="AB4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customFormat="1" customHeight="1" s="3">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="3" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>msr_pointpillar</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="11" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>[x,y,z,dop_x_gnd,dop_y_gnd,rcs]</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>PN[64]</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>PP[3,5,5]*[64,128,256]</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>UPSAMPLE[1,2,4]+CONCAT[384]</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>anchorbased</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>NMS[gpu,0.1,mc]</t>
+        </is>
+      </c>
       <c r="L5" s="11" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38.748G</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4.861M</t>
+        </is>
+      </c>
       <c r="O5" s="20" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="3" t="n"/>
-      <c r="U5" s="3" t="inlineStr"/>
+      <c r="P5" s="2" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>64.83</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="11" t="n"/>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" s="3" t="n"/>
-      <c r="Y5" s="3" t="n"/>
-      <c r="Z5" s="3" t="n"/>
-      <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="W5" s="2" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>77.45999999999999</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>86.61</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customFormat="1" customHeight="1" s="3">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="3" t="n"/>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="11" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
       <c r="L6" s="11" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
       <c r="O6" s="20" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n"/>
-      <c r="T6" s="3" t="n"/>
-      <c r="U6" s="3" t="inlineStr"/>
+      <c r="P6" s="2" t="n">
+        <v>90.26000000000001</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>96.19</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>97.20999999999999</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="11" t="n"/>
-      <c r="W6" s="3" t="n"/>
-      <c r="X6" s="3" t="n"/>
-      <c r="Y6" s="3" t="n"/>
-      <c r="Z6" s="3" t="n"/>
-      <c r="AA6" s="3" t="n"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customFormat="1" customHeight="1" s="3">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="3" t="n"/>
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="11" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
       <c r="L7" s="11" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
       <c r="O7" s="20" t="n"/>
-      <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="n"/>
-      <c r="T7" s="3" t="n"/>
-      <c r="U7" s="3" t="inlineStr"/>
+      <c r="P7" s="2" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>67.62</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>72.58</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="11" t="n"/>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" s="3" t="n"/>
-      <c r="Y7" s="3" t="n"/>
-      <c r="Z7" s="3" t="n"/>
-      <c r="AA7" s="3" t="n"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customFormat="1" customHeight="1" s="3">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="14" t="n"/>
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="11" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="3" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
       <c r="L8" s="11" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
       <c r="O8" s="20" t="n"/>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="n"/>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
+      <c r="P8" s="2" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="U8" s="2" t="n"/>
       <c r="V8" s="11" t="n"/>
-      <c r="W8" s="3" t="n"/>
-      <c r="X8" s="3" t="n"/>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
-      <c r="AA8" s="3" t="n"/>
+      <c r="W8" s="2" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>98.70999999999999</v>
+      </c>
+      <c r="AB8" s="2" t="n"/>
     </row>
     <row r="9" ht="18" customFormat="1" customHeight="1" s="3">
       <c r="A9" s="3" t="n"/>
